--- a/ig/DM-SEPTEMBRE-2026/ValueSet-JDV-J218-CNAMAmeliSecteurConventionnement-ROR.xlsx
+++ b/ig/DM-SEPTEMBRE-2026/ValueSet-JDV-J218-CNAMAmeliSecteurConventionnement-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="46">
   <si>
     <t>Property</t>
   </si>
@@ -129,13 +129,19 @@
     <t>1</t>
   </si>
   <si>
+    <t>Conventionné</t>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
-    <t>Conventionné Dépassement Permanent</t>
+    <t>Conventionné avec dépassement</t>
   </si>
   <si>
     <t>3</t>
+  </si>
+  <si>
+    <t>Conventionné avec honoraires libres</t>
   </si>
   <si>
     <t/>
@@ -466,39 +472,39 @@
         <v>37</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>31</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
